--- a/data/B24_department_schedules_finals/faculty_schedule_manuel_finals.xlsx
+++ b/data/B24_department_schedules_finals/faculty_schedule_manuel_finals.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/B24_department_schedules_finals/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_48D5A2E2ED9BCD30632D4C0F9DEC09A579798194" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FACF0571-4E68-445A-B0B0-6E9B3E12A310}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="20760" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -925,8 +931,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -989,13 +995,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1033,7 +1047,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1067,6 +1081,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1101,9 +1116,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1276,11 +1292,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H220"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="5" max="5" width="34" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1306,7 +1325,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1332,7 +1351,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1358,7 +1377,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1384,7 +1403,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1410,7 +1429,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1436,7 +1455,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1462,7 +1481,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1488,7 +1507,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1514,7 +1533,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1540,7 +1559,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -1566,7 +1585,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1592,7 +1611,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -1618,7 +1637,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1644,7 +1663,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1670,7 +1689,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -1696,7 +1715,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -1722,7 +1741,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -1748,7 +1767,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -1774,7 +1793,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -1800,7 +1819,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -1826,7 +1845,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -1852,7 +1871,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>13</v>
       </c>
@@ -1878,7 +1897,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -1904,7 +1923,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -1930,7 +1949,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>13</v>
       </c>
@@ -1956,7 +1975,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>13</v>
       </c>
@@ -1982,7 +2001,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -2008,7 +2027,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>11</v>
       </c>
@@ -2034,7 +2053,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -2060,7 +2079,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>13</v>
       </c>
@@ -2086,7 +2105,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>14</v>
       </c>
@@ -2112,7 +2131,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -2138,7 +2157,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -2164,7 +2183,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -2190,7 +2209,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>13</v>
       </c>
@@ -2216,7 +2235,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>13</v>
       </c>
@@ -2242,7 +2261,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -2268,7 +2287,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>13</v>
       </c>
@@ -2294,7 +2313,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>13</v>
       </c>
@@ -2320,7 +2339,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>12</v>
       </c>
@@ -2346,7 +2365,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>15</v>
       </c>
@@ -2372,7 +2391,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>12</v>
       </c>
@@ -2398,7 +2417,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>11</v>
       </c>
@@ -2424,7 +2443,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>11</v>
       </c>
@@ -2450,7 +2469,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>11</v>
       </c>
@@ -2476,7 +2495,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -2502,7 +2521,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>14</v>
       </c>
@@ -2528,7 +2547,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>14</v>
       </c>
@@ -2554,7 +2573,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>13</v>
       </c>
@@ -2580,7 +2599,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>13</v>
       </c>
@@ -2606,7 +2625,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>11</v>
       </c>
@@ -2632,7 +2651,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>12</v>
       </c>
@@ -2658,7 +2677,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>14</v>
       </c>
@@ -2684,7 +2703,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>11</v>
       </c>
@@ -2710,7 +2729,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>15</v>
       </c>
@@ -2736,7 +2755,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>14</v>
       </c>
@@ -2762,7 +2781,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>14</v>
       </c>
@@ -2788,7 +2807,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>12</v>
       </c>
@@ -2814,7 +2833,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>12</v>
       </c>
@@ -2840,7 +2859,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>14</v>
       </c>
@@ -2866,7 +2885,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>11</v>
       </c>
@@ -2892,7 +2911,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>8</v>
       </c>
@@ -2918,7 +2937,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>8</v>
       </c>
@@ -2944,7 +2963,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>14</v>
       </c>
@@ -2970,7 +2989,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>13</v>
       </c>
@@ -2996,7 +3015,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>11</v>
       </c>
@@ -3022,7 +3041,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>14</v>
       </c>
@@ -3048,7 +3067,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>8</v>
       </c>
@@ -3074,7 +3093,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>8</v>
       </c>
@@ -3100,7 +3119,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>13</v>
       </c>
@@ -3126,7 +3145,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>12</v>
       </c>
@@ -3152,7 +3171,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>13</v>
       </c>
@@ -3178,7 +3197,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>11</v>
       </c>
@@ -3204,7 +3223,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>8</v>
       </c>
@@ -3230,7 +3249,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>14</v>
       </c>
@@ -3256,7 +3275,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>13</v>
       </c>
@@ -3282,7 +3301,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>13</v>
       </c>
@@ -3308,7 +3327,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>16</v>
       </c>
@@ -3334,7 +3353,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>14</v>
       </c>
@@ -3360,7 +3379,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>12</v>
       </c>
@@ -3386,7 +3405,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>8</v>
       </c>
@@ -3412,7 +3431,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>8</v>
       </c>
@@ -3438,7 +3457,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>14</v>
       </c>
@@ -3464,7 +3483,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>14</v>
       </c>
@@ -3490,7 +3509,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>13</v>
       </c>
@@ -3516,7 +3535,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>13</v>
       </c>
@@ -3542,7 +3561,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>8</v>
       </c>
@@ -3568,7 +3587,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>14</v>
       </c>
@@ -3594,7 +3613,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>12</v>
       </c>
@@ -3620,7 +3639,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>14</v>
       </c>
@@ -3646,7 +3665,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>8</v>
       </c>
@@ -3672,7 +3691,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>14</v>
       </c>
@@ -3698,7 +3717,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>8</v>
       </c>
@@ -3724,7 +3743,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>8</v>
       </c>
@@ -3750,7 +3769,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>14</v>
       </c>
@@ -3776,7 +3795,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>14</v>
       </c>
@@ -3802,7 +3821,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>8</v>
       </c>
@@ -3828,7 +3847,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>8</v>
       </c>
@@ -3854,7 +3873,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>14</v>
       </c>
@@ -3880,7 +3899,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>13</v>
       </c>
@@ -3906,7 +3925,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>12</v>
       </c>
@@ -3932,7 +3951,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>12</v>
       </c>
@@ -3958,7 +3977,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>8</v>
       </c>
@@ -3984,7 +4003,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>13</v>
       </c>
@@ -4010,7 +4029,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>12</v>
       </c>
@@ -4036,7 +4055,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>8</v>
       </c>
@@ -4062,7 +4081,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>14</v>
       </c>
@@ -4088,7 +4107,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>8</v>
       </c>
@@ -4114,7 +4133,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>8</v>
       </c>
@@ -4140,7 +4159,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>14</v>
       </c>
@@ -4166,7 +4185,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>12</v>
       </c>
@@ -4192,7 +4211,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>8</v>
       </c>
@@ -4218,7 +4237,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>14</v>
       </c>
@@ -4244,7 +4263,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>12</v>
       </c>
@@ -4270,7 +4289,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>14</v>
       </c>
@@ -4296,7 +4315,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>14</v>
       </c>
@@ -4322,7 +4341,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>14</v>
       </c>
@@ -4348,7 +4367,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>14</v>
       </c>
@@ -4374,7 +4393,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>14</v>
       </c>
@@ -4400,7 +4419,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>14</v>
       </c>
@@ -4426,7 +4445,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>14</v>
       </c>
@@ -4452,7 +4471,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>14</v>
       </c>
@@ -4478,7 +4497,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>13</v>
       </c>
@@ -4504,7 +4523,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>12</v>
       </c>
@@ -4530,7 +4549,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>14</v>
       </c>
@@ -4556,7 +4575,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>12</v>
       </c>
@@ -4582,7 +4601,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>8</v>
       </c>
@@ -4608,7 +4627,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>14</v>
       </c>
@@ -4634,7 +4653,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>11</v>
       </c>
@@ -4660,7 +4679,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>14</v>
       </c>
@@ -4686,7 +4705,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>8</v>
       </c>
@@ -4712,7 +4731,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>13</v>
       </c>
@@ -4738,7 +4757,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>12</v>
       </c>
@@ -4764,7 +4783,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>14</v>
       </c>
@@ -4790,7 +4809,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>13</v>
       </c>
@@ -4816,7 +4835,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>8</v>
       </c>
@@ -4842,7 +4861,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>8</v>
       </c>
@@ -4868,7 +4887,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>14</v>
       </c>
@@ -4894,7 +4913,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>13</v>
       </c>
@@ -4920,7 +4939,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>13</v>
       </c>
@@ -4946,7 +4965,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>11</v>
       </c>
@@ -4972,7 +4991,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>12</v>
       </c>
@@ -4998,7 +5017,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>8</v>
       </c>
@@ -5024,7 +5043,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>13</v>
       </c>
@@ -5050,7 +5069,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>17</v>
       </c>
@@ -5076,7 +5095,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>13</v>
       </c>
@@ -5102,7 +5121,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>11</v>
       </c>
@@ -5128,7 +5147,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>13</v>
       </c>
@@ -5154,7 +5173,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>13</v>
       </c>
@@ -5180,7 +5199,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>11</v>
       </c>
@@ -5206,7 +5225,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>11</v>
       </c>
@@ -5232,7 +5251,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>11</v>
       </c>
@@ -5258,7 +5277,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>11</v>
       </c>
@@ -5284,7 +5303,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>17</v>
       </c>
@@ -5310,7 +5329,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>17</v>
       </c>
@@ -5336,7 +5355,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>12</v>
       </c>
@@ -5362,7 +5381,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>11</v>
       </c>
@@ -5388,7 +5407,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>11</v>
       </c>
@@ -5414,7 +5433,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>11</v>
       </c>
@@ -5440,7 +5459,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="161" spans="1:8">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>17</v>
       </c>
@@ -5466,7 +5485,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>17</v>
       </c>
@@ -5492,7 +5511,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="163" spans="1:8">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>17</v>
       </c>
@@ -5518,7 +5537,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="164" spans="1:8">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>17</v>
       </c>
@@ -5544,7 +5563,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="165" spans="1:8">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>11</v>
       </c>
@@ -5570,7 +5589,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>11</v>
       </c>
@@ -5596,7 +5615,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>11</v>
       </c>
@@ -5622,7 +5641,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="168" spans="1:8">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>11</v>
       </c>
@@ -5648,7 +5667,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="169" spans="1:8">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>11</v>
       </c>
@@ -5674,7 +5693,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>11</v>
       </c>
@@ -5700,7 +5719,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>11</v>
       </c>
@@ -5726,7 +5745,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>17</v>
       </c>
@@ -5752,7 +5771,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>18</v>
       </c>
@@ -5778,7 +5797,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="174" spans="1:8">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>11</v>
       </c>
@@ -5804,7 +5823,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>11</v>
       </c>
@@ -5830,7 +5849,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="176" spans="1:8">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>17</v>
       </c>
@@ -5856,7 +5875,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>17</v>
       </c>
@@ -5882,7 +5901,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>17</v>
       </c>
@@ -5908,7 +5927,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>13</v>
       </c>
@@ -5934,7 +5953,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="180" spans="1:8">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>13</v>
       </c>
@@ -5960,7 +5979,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>11</v>
       </c>
@@ -5986,7 +6005,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="182" spans="1:8">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>19</v>
       </c>
@@ -6012,7 +6031,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>17</v>
       </c>
@@ -6038,7 +6057,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="184" spans="1:8">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>17</v>
       </c>
@@ -6064,7 +6083,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="185" spans="1:8">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>8</v>
       </c>
@@ -6090,7 +6109,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="186" spans="1:8">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>8</v>
       </c>
@@ -6116,7 +6135,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="187" spans="1:8">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>11</v>
       </c>
@@ -6142,7 +6161,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="188" spans="1:8">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>17</v>
       </c>
@@ -6168,7 +6187,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="189" spans="1:8">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>12</v>
       </c>
@@ -6194,7 +6213,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="190" spans="1:8">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>18</v>
       </c>
@@ -6220,7 +6239,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="191" spans="1:8">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>12</v>
       </c>
@@ -6246,7 +6265,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="192" spans="1:8">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>18</v>
       </c>
@@ -6272,7 +6291,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="193" spans="1:8">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>17</v>
       </c>
@@ -6298,7 +6317,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="194" spans="1:8">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>17</v>
       </c>
@@ -6324,7 +6343,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="195" spans="1:8">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>17</v>
       </c>
@@ -6350,7 +6369,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="196" spans="1:8">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>12</v>
       </c>
@@ -6376,7 +6395,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>17</v>
       </c>
@@ -6402,7 +6421,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>17</v>
       </c>
@@ -6428,7 +6447,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>18</v>
       </c>
@@ -6454,7 +6473,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>18</v>
       </c>
@@ -6480,7 +6499,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>18</v>
       </c>
@@ -6506,7 +6525,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
         <v>17</v>
       </c>
@@ -6532,7 +6551,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="203" spans="1:8">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
         <v>18</v>
       </c>
@@ -6558,7 +6577,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="204" spans="1:8">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
         <v>18</v>
       </c>
@@ -6584,7 +6603,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="205" spans="1:8">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
         <v>18</v>
       </c>
@@ -6610,7 +6629,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="206" spans="1:8">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
         <v>18</v>
       </c>
@@ -6636,7 +6655,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="207" spans="1:8">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
         <v>18</v>
       </c>
@@ -6662,7 +6681,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="208" spans="1:8">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
         <v>17</v>
       </c>
@@ -6688,7 +6707,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="209" spans="1:8">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
         <v>17</v>
       </c>
@@ -6714,7 +6733,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="210" spans="1:8">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
         <v>18</v>
       </c>
@@ -6740,7 +6759,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="211" spans="1:8">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
         <v>18</v>
       </c>
@@ -6766,7 +6785,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="212" spans="1:8">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
         <v>18</v>
       </c>
@@ -6792,7 +6811,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="213" spans="1:8">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
         <v>18</v>
       </c>
@@ -6818,7 +6837,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="214" spans="1:8">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
         <v>18</v>
       </c>
@@ -6844,7 +6863,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="215" spans="1:8">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
         <v>17</v>
       </c>
@@ -6870,7 +6889,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="216" spans="1:8">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
         <v>18</v>
       </c>
@@ -6896,7 +6915,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:8">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
         <v>18</v>
       </c>
@@ -6922,7 +6941,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:8">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
         <v>18</v>
       </c>
@@ -6948,7 +6967,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
         <v>18</v>
       </c>
@@ -6974,7 +6993,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="220" spans="1:8">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
         <v>12</v>
       </c>
